--- a/26MMS0139-CISCO-Attendance Roster_Splunk Basics_12-14 May.xlsx
+++ b/26MMS0139-CISCO-Attendance Roster_Splunk Basics_12-14 May.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rpsconsulting-my.sharepoint.com/personal/arunkumar_h_rpsconsulting_in/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\SPLK_CISCO_US_12_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{2F5C526C-6E03-4769-8BC1-02E2D2E8674A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92456500-696A-478C-819C-E86014E4F788}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06F9AD-3048-4AD9-9BCF-F700BC0FC644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
   <si>
     <t>Start Date</t>
   </si>
@@ -132,6 +130,12 @@
   </si>
   <si>
     <t>aislas@cisco.com</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -409,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -468,23 +472,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,23 +768,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="23"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>0</v>
@@ -793,7 +794,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>1</v>
@@ -803,7 +804,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
         <v>2</v>
@@ -813,7 +814,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="8" t="s">
         <v>3</v>
@@ -823,27 +824,27 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>5</v>
       </c>
@@ -860,137 +861,185 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="12"/>
+      <c r="C12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="E12" s="12"/>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="13"/>
+      <c r="C13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="E13" s="12"/>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="22" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="13"/>
+      <c r="C15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="E15" s="12"/>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="22" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="10"/>
+      <c r="C16" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="E16" s="12"/>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="E19" s="12"/>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="10"/>
+      <c r="C20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="E21" s="12"/>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="22" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="E22" s="12"/>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24" t="s">
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="22" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="25"/>
+      <c r="C23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="23"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:B23">

--- a/26MMS0139-CISCO-Attendance Roster_Splunk Basics_12-14 May.xlsx
+++ b/26MMS0139-CISCO-Attendance Roster_Splunk Basics_12-14 May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\SPLK_CISCO_US_12_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06F9AD-3048-4AD9-9BCF-F700BC0FC644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77379527-DBEB-48E3-9B8E-5C935E3737C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="34">
   <si>
     <t>Start Date</t>
   </si>
@@ -874,7 +874,9 @@
       <c r="D12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
@@ -889,7 +891,9 @@
       <c r="D13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
@@ -904,7 +908,9 @@
       <c r="D14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="12"/>
+      <c r="E14" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
@@ -919,7 +925,9 @@
       <c r="D15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="12"/>
+      <c r="E15" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
@@ -934,7 +942,9 @@
       <c r="D16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
@@ -949,7 +959,9 @@
       <c r="D17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
@@ -964,7 +976,9 @@
       <c r="D18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
@@ -979,7 +993,9 @@
       <c r="D19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
@@ -994,7 +1010,9 @@
       <c r="D20" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
@@ -1009,7 +1027,9 @@
       <c r="D21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="12"/>
+      <c r="E21" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
@@ -1024,7 +1044,9 @@
       <c r="D22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="12"/>
+      <c r="E22" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
@@ -1039,7 +1061,9 @@
       <c r="D23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="23"/>
+      <c r="E23" s="23" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:B23">
